--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F271204-687D-4EDD-ABCC-1447D1A001D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="2320" windowWidth="20000" windowHeight="14000" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
   <sheets>
     <sheet name="exportCategories" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>TaxRates</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Gratta E Vinci</t>
+  </si>
+  <si>
+    <t>DEA</t>
+  </si>
+  <si>
+    <t>VAPORART</t>
   </si>
 </sst>
 </file>
@@ -979,8 +985,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE833D4-1625-42DF-AF1B-9BE862AB68C2}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1593,6 +1603,34 @@
       </c>
       <c r="N20">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e00ee7abe3ef944f/Progetto Ubify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3748662-1C4B-472D-89E4-DCF8E5441202}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
   <sheets>
     <sheet name="exportCategories" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>TaxRates</t>
   </si>
@@ -125,6 +125,21 @@
   </si>
   <si>
     <t>VAPORART</t>
+  </si>
+  <si>
+    <t>Giochi e Vincite</t>
+  </si>
+  <si>
+    <t>Perfetti Van Melle</t>
+  </si>
+  <si>
+    <t>DINNER LADY FAM LTD</t>
+  </si>
+  <si>
+    <t>Vapour Italia S.r.l.</t>
+  </si>
+  <si>
+    <t>LOGISTA RETAIL ITALIA S.P.A.</t>
   </si>
 </sst>
 </file>
@@ -985,14 +1000,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE833D4-1625-42DF-AF1B-9BE862AB68C2}">
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1053,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>22</v>
       </c>
@@ -1068,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>22</v>
       </c>
@@ -1106,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>22</v>
       </c>
@@ -1144,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1179,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1205,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1231,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1257,7 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1283,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1309,7 +1326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>22</v>
       </c>
@@ -1338,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1367,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>22</v>
       </c>
@@ -1402,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>22</v>
       </c>
@@ -1431,7 +1448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>22</v>
       </c>
@@ -1460,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>22</v>
       </c>
@@ -1489,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>22</v>
       </c>
@@ -1518,7 +1535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
@@ -1547,7 +1564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0</v>
       </c>
@@ -1576,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0</v>
       </c>
@@ -1605,7 +1622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>22</v>
       </c>
@@ -1619,7 +1636,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1631,6 +1648,90 @@
       </c>
       <c r="E22" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e00ee7abe3ef944f/Progetto Ubify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3748662-1C4B-472D-89E4-DCF8E5441202}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE8071E-D919-4EAA-9E54-8CCC6435F7C6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>TaxRates</t>
   </si>
@@ -140,6 +140,12 @@
   </si>
   <si>
     <t>LOGISTA RETAIL ITALIA S.P.A.</t>
+  </si>
+  <si>
+    <t>Itaexpress</t>
+  </si>
+  <si>
+    <t>SvapoEBasta</t>
   </si>
 </sst>
 </file>
@@ -681,6 +687,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE833D4-1625-42DF-AF1B-9BE862AB68C2}">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
@@ -1734,6 +1744,34 @@
         <v>39</v>
       </c>
     </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e00ee7abe3ef944f/Progetto Ubify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{41D3A892-0795-45C1-9489-DBD5A79C3F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE8071E-D919-4EAA-9E54-8CCC6435F7C6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E295F-201E-48C3-839E-A36C4899E7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="19995" windowHeight="13995" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
   <sheets>
     <sheet name="exportCategories" sheetId="1" r:id="rId1"/>
@@ -687,10 +687,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1664,28 +1660,28 @@
       <c r="A23">
         <v>0</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
         <v>35</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
+      <c r="G23">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0</v>
       </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">

--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E295F-201E-48C3-839E-A36C4899E7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C902BCFF-84A5-492D-A8FB-CD2365B8DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="19995" windowHeight="13995" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
+    <workbookView xWindow="7230" yWindow="2600" windowWidth="20000" windowHeight="14000" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
   <sheets>
     <sheet name="exportCategories" sheetId="1" r:id="rId1"/>
@@ -1007,15 +1007,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE833D4-1625-42DF-AF1B-9BE862AB68C2}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>22</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>22</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>22</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>22</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1390,9 +1390,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>22</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>22</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>22</v>
       </c>
@@ -1512,9 +1512,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>22</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>0</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>0</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>22</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>0</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>0</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>22</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>22</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>22</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>22</v>
       </c>
@@ -1754,9 +1754,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>

--- a/exportCategories.xlsx
+++ b/exportCategories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C902BCFF-84A5-492D-A8FB-CD2365B8DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D228FDBB-1C5F-4C87-A2EB-EE8B6E4BED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="2600" windowWidth="20000" windowHeight="14000" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
+    <workbookView xWindow="4370" yWindow="6520" windowWidth="31360" windowHeight="14000" xr2:uid="{C88CECE9-AF8B-4910-9389-7B90E4126F09}"/>
   </bookViews>
   <sheets>
     <sheet name="exportCategories" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>TaxRates</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>SvapoEBasta</t>
+  </si>
+  <si>
+    <t>Ferrero</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE833D4-1625-42DF-AF1B-9BE862AB68C2}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.81640625" customWidth="1"/>
@@ -1395,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -1517,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -1692,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -1766,6 +1769,20 @@
       </c>
       <c r="E30" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
